--- a/Result/profitability/3265.xlsx
+++ b/Result/profitability/3265.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.23</v>
       </c>
       <c r="M2" t="n">
-        <v>1.2875</v>
+        <v>1.38875</v>
       </c>
       <c r="N2" t="n">
-        <v>25.3875</v>
+        <v>26.06125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.32</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1675</v>
+        <v>1.235</v>
       </c>
       <c r="N3" t="n">
-        <v>25.20625</v>
+        <v>25.60125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.37</v>
       </c>
       <c r="M4" t="n">
-        <v>1.02</v>
+        <v>1.08875</v>
       </c>
       <c r="N4" t="n">
-        <v>25.6675</v>
+        <v>25.745</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.23</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7987500000000001</v>
+        <v>0.9775</v>
       </c>
       <c r="N5" t="n">
-        <v>20.8075</v>
+        <v>21.05625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.23</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6875</v>
+        <v>0.7575</v>
       </c>
       <c r="N6" t="n">
-        <v>9.671249999999997</v>
+        <v>10.44875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.49625</v>
+        <v>0.53875</v>
       </c>
       <c r="N7" t="n">
-        <v>8.824999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.27</v>
       </c>
       <c r="M8" t="n">
-        <v>0.31125</v>
+        <v>0.3525</v>
       </c>
       <c r="N8" t="n">
-        <v>9.89875</v>
+        <v>10.37625</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3265</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1408</v>
+      </c>
+      <c r="D75" t="n">
+        <v>994</v>
+      </c>
+      <c r="E75" t="n">
+        <v>413</v>
+      </c>
+      <c r="F75" t="n">
+        <v>29.37</v>
+      </c>
+      <c r="G75" t="n">
+        <v>338</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>24.01%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-8</v>
+      </c>
+      <c r="J75" t="n">
+        <v>330</v>
+      </c>
+      <c r="K75" t="n">
+        <v>285</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="N75" t="n">
+        <v>26.295</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.3299999999999998</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1495107632093933</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>2.166666666666667</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.990000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.07268078889700513</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
